--- a/rtss-pre1917/charts/birth-death-counts/Воронежская.xlsx
+++ b/rtss-pre1917/charts/birth-death-counts/Воронежская.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13217662-7D9F-4E6D-A5CD-8949F44F22A1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E1A47A2-FF2B-43C1-8331-E28057919178}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13050" yWindow="2160" windowWidth="24945" windowHeight="21255" xr2:uid="{552C350D-897F-4D5C-BE01-5853E10F71A5}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" xr2:uid="{552C350D-897F-4D5C-BE01-5853E10F71A5}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -149,21 +149,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1478,12 +1486,12 @@
             <c:numRef>
               <c:f>data!$G$6:$G$40</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="35"/>
-                <c:pt idx="5" formatCode="#,##0">
+                <c:pt idx="5">
                   <c:v>1200</c:v>
                 </c:pt>
-                <c:pt idx="6" formatCode="#,##0">
+                <c:pt idx="6">
                   <c:v>1500</c:v>
                 </c:pt>
                 <c:pt idx="7">
@@ -1656,12 +1664,12 @@
             <c:numRef>
               <c:f>data!$H$6:$H$40</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="35"/>
-                <c:pt idx="5" formatCode="#,##0">
+                <c:pt idx="5">
                   <c:v>1350</c:v>
                 </c:pt>
-                <c:pt idx="6" formatCode="#,##0">
+                <c:pt idx="6">
                   <c:v>1200</c:v>
                 </c:pt>
               </c:numCache>
@@ -1852,12 +1860,12 @@
             <c:numRef>
               <c:f>data!$I$6:$I$40</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="35"/>
-                <c:pt idx="5" formatCode="#,##0">
+                <c:pt idx="5">
                   <c:v>900</c:v>
                 </c:pt>
-                <c:pt idx="6" formatCode="#,##0">
+                <c:pt idx="6">
                   <c:v>1200</c:v>
                 </c:pt>
               </c:numCache>
@@ -2024,9 +2032,9 @@
             <c:numRef>
               <c:f>data!$J$6:$J$40</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="35"/>
-                <c:pt idx="5" formatCode="#,##0">
+                <c:pt idx="5">
                   <c:v>1250</c:v>
                 </c:pt>
                 <c:pt idx="6">
@@ -3203,15 +3211,27 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
+    <row r="2" spans="1:34">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+    </row>
     <row r="3" spans="1:34" ht="15.75">
-      <c r="A3" s="4"/>
+      <c r="A3" s="7"/>
       <c r="B3" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="4"/>
+      <c r="F3" s="7"/>
       <c r="G3" s="8" t="s">
         <v>14</v>
       </c>
@@ -3220,7 +3240,7 @@
       <c r="J3" s="8"/>
     </row>
     <row r="4" spans="1:34" ht="15.75">
-      <c r="A4" s="4"/>
+      <c r="A4" s="7"/>
       <c r="B4" s="8" t="s">
         <v>6</v>
       </c>
@@ -3229,7 +3249,7 @@
         <v>7</v>
       </c>
       <c r="E4" s="8"/>
-      <c r="F4" s="4"/>
+      <c r="F4" s="7"/>
       <c r="G4" s="8" t="s">
         <v>6</v>
       </c>
@@ -3240,30 +3260,30 @@
       <c r="J4" s="8"/>
     </row>
     <row r="5" spans="1:34" ht="15.75">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="7"/>
+      <c r="B5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="5" t="s">
+      <c r="F5" s="7"/>
+      <c r="G5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="9" t="s">
         <v>12</v>
       </c>
       <c r="AE5" s="3"/>
@@ -3272,1220 +3292,944 @@
       <c r="AH5" s="3"/>
     </row>
     <row r="6" spans="1:34" ht="15.75">
-      <c r="A6" s="6">
+      <c r="A6" s="10">
         <v>1880</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7" t="n">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5" t="n">
         <v>120269.0</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="5" t="n">
         <v>94118.0</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="7"/>
+      <c r="G6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="4" t="n">
-        <v>120269.0</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>94118.0</v>
-      </c>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
       <c r="AG6" s="3"/>
       <c r="AH6" s="3"/>
     </row>
     <row r="7" spans="1:34" ht="15.75">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="10" t="n">
         <f>A6+1</f>
         <v>1881.0</v>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="5" t="n">
         <v>121033.0</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="5" t="n">
         <v>84188.0</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="5" t="n">
         <v>121854.0</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="5" t="n">
         <v>85244.0</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4" t="n">
-        <v>121033.0</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>84188.0</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>121854.0</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>85244.0</v>
-      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
       <c r="AE7" s="3"/>
       <c r="AF7" s="3"/>
       <c r="AG7" s="3"/>
       <c r="AH7" s="3"/>
     </row>
     <row r="8" spans="1:34" ht="15.75">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="10" t="n">
         <f t="shared" ref="A8:A40" si="0">A7+1</f>
         <v>1882.0</v>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="5" t="n">
         <v>127594.0</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="5" t="n">
         <v>120861.0</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="5" t="n">
         <v>127159.0</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="5" t="n">
         <v>120047.0</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4" t="n">
-        <v>127594.0</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>120861.0</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>127159.0</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>120047.0</v>
-      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
       <c r="AE8" s="3"/>
       <c r="AF8" s="3"/>
       <c r="AG8" s="3"/>
       <c r="AH8" s="3"/>
     </row>
     <row r="9" spans="1:34" ht="15.75">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1883.0</v>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="5" t="n">
         <v>127465.0</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="5" t="n">
         <v>95156.0</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="5" t="n">
         <v>127922.0</v>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="E9" s="5" t="n">
         <v>94065.0</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4" t="n">
-        <v>127465.0</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>95156.0</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>127922.0</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>94065.0</v>
-      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
       <c r="AE9" s="3"/>
       <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
     </row>
     <row r="10" spans="1:34" ht="15.75">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1884.0</v>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="5" t="n">
         <v>130682.0</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="5" t="n">
         <v>76983.0</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="5" t="n">
         <v>130007.0</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E10" s="5" t="n">
         <v>77111.0</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4" t="n">
-        <v>130682.0</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>76983.0</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>130007.0</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>77111.0</v>
-      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
       <c r="AE10" s="3"/>
       <c r="AF10" s="3"/>
       <c r="AG10" s="3"/>
       <c r="AH10" s="3"/>
     </row>
     <row r="11" spans="1:34" ht="15.75">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1885.0</v>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="5" t="n">
         <v>126328.0</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="5" t="n">
         <v>84170.0</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="5" t="n">
         <v>126324.0</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" s="5" t="n">
         <v>83638.0</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="7" t="n">
-        <v>126328.0</v>
-      </c>
-      <c r="H11" s="7" t="n">
-        <v>84170.0</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>126324.0</v>
-      </c>
-      <c r="J11" s="7" t="n">
-        <v>83638.0</v>
-      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
     </row>
     <row r="12" spans="1:34" ht="15.75">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1886.0</v>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="5" t="n">
         <v>129470.0</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="5" t="n">
         <v>85745.0</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="5" t="n">
         <v>129095.0</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" s="5" t="n">
         <v>85410.0</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="7" t="n">
-        <v>129470.0</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>85745.0</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>129095.0</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>85410.0</v>
-      </c>
+      <c r="F12" s="7"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
       <c r="AE12" s="3"/>
       <c r="AF12" s="3"/>
       <c r="AG12" s="3"/>
       <c r="AH12" s="3"/>
     </row>
     <row r="13" spans="1:34" ht="15.75">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1887.0</v>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="5" t="n">
         <v>130763.0</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="5" t="n">
         <v>91682.0</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="5" t="n">
         <v>132120.0</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" s="5" t="n">
         <v>92510.0</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4" t="n">
-        <v>130763.0</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>91682.0</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>132120.0</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>92510.0</v>
-      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
       <c r="AE13" s="3"/>
       <c r="AF13" s="3"/>
       <c r="AG13" s="3"/>
       <c r="AH13" s="3"/>
     </row>
     <row r="14" spans="1:34" ht="15.75">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1888.0</v>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="5" t="n">
         <v>139267.0</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="5" t="n">
         <v>89062.0</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="5" t="n">
         <v>141268.0</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E14" s="5" t="n">
         <v>90117.0</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4" t="n">
-        <v>139267.0</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>89062.0</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>141268.0</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>90117.0</v>
-      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
       <c r="AG14" s="3"/>
       <c r="AH14" s="3"/>
     </row>
     <row r="15" spans="1:34" ht="15.75">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1889.0</v>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="5" t="n">
         <v>146471.0</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="5" t="n">
         <v>107043.0</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="5" t="n">
         <v>146534.0</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E15" s="5" t="n">
         <v>106945.0</v>
       </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4" t="n">
-        <v>146471.0</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>107043.0</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>146534.0</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>106945.0</v>
-      </c>
+      <c r="F15" s="7"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
       <c r="AE15" s="3"/>
       <c r="AF15" s="3"/>
       <c r="AG15" s="3"/>
       <c r="AH15" s="3"/>
     </row>
     <row r="16" spans="1:34" ht="15.75">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1890.0</v>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="5" t="n">
         <v>134898.0</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="5" t="n">
         <v>107953.0</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="5" t="n">
         <v>134296.0</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="E16" s="5" t="n">
         <v>108852.0</v>
       </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4" t="n">
-        <v>134898.0</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>107953.0</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>134296.0</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>108852.0</v>
-      </c>
+      <c r="F16" s="7"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
     </row>
     <row r="17" spans="1:34" ht="15.75">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1891.0</v>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="5" t="n">
         <v>149416.0</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="5" t="n">
         <v>118774.0</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="5" t="n">
         <v>148177.0</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="E17" s="5" t="n">
         <v>116940.0</v>
       </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4" t="n">
-        <v>149416.0</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>118774.0</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>148177.0</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>116940.0</v>
-      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
       <c r="AE17" s="3"/>
       <c r="AF17" s="3"/>
       <c r="AG17" s="3"/>
       <c r="AH17" s="3"/>
     </row>
     <row r="18" spans="1:34" ht="15.75">
-      <c r="A18" s="6" t="n">
+      <c r="A18" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1892.0</v>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B18" s="5" t="n">
         <v>116448.0</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="5" t="n">
         <v>152129.0</v>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="5" t="n">
         <v>117373.0</v>
       </c>
-      <c r="E18" s="7" t="n">
+      <c r="E18" s="5" t="n">
         <v>152270.0</v>
       </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4" t="n">
-        <v>116448.0</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>152129.0</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>117373.0</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>152270.0</v>
-      </c>
+      <c r="F18" s="7"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
       <c r="AE18" s="3"/>
       <c r="AF18" s="3"/>
       <c r="AG18" s="3"/>
       <c r="AH18" s="3"/>
     </row>
     <row r="19" spans="1:34" ht="15.75">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1893.0</v>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B19" s="5" t="n">
         <v>140311.0</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="5" t="n">
         <v>97045.0</v>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D19" s="5" t="n">
         <v>141101.0</v>
       </c>
-      <c r="E19" s="7" t="n">
+      <c r="E19" s="5" t="n">
         <v>96974.0</v>
       </c>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4" t="n">
-        <v>140311.0</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>97045.0</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>141101.0</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>96974.0</v>
-      </c>
+      <c r="F19" s="7"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
     </row>
     <row r="20" spans="1:34" ht="15.75">
-      <c r="A20" s="6" t="n">
+      <c r="A20" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1894.0</v>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="B20" s="5" t="n">
         <v>139422.0</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="5" t="n">
         <v>105538.0</v>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="5" t="n">
         <v>140568.0</v>
       </c>
-      <c r="E20" s="7" t="n">
+      <c r="E20" s="5" t="n">
         <v>105997.0</v>
       </c>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4" t="n">
-        <v>139422.0</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>105538.0</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>140568.0</v>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>105997.0</v>
-      </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
       <c r="AE20" s="3"/>
       <c r="AF20" s="3"/>
       <c r="AG20" s="3"/>
       <c r="AH20" s="3"/>
     </row>
     <row r="21" spans="1:34" ht="15.75">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1895.0</v>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B21" s="5" t="n">
         <v>142665.0</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="5" t="n">
         <v>119761.0</v>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="5" t="n">
         <v>144525.0</v>
       </c>
-      <c r="E21" s="7" t="n">
+      <c r="E21" s="5" t="n">
         <v>120613.0</v>
       </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4" t="n">
-        <v>142665.0</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>119761.0</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>144525.0</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>120613.0</v>
-      </c>
+      <c r="F21" s="7"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
       <c r="AE21" s="3"/>
       <c r="AF21" s="3"/>
       <c r="AG21" s="3"/>
       <c r="AH21" s="3"/>
     </row>
     <row r="22" spans="1:34" ht="15.75">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1896.0</v>
       </c>
-      <c r="B22" s="7" t="n">
+      <c r="B22" s="5" t="n">
         <v>149557.0</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="5" t="n">
         <v>109668.0</v>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="5" t="n">
         <v>151978.0</v>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E22" s="5" t="n">
         <v>110891.0</v>
       </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4" t="n">
-        <v>149557.0</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>109668.0</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>151978.0</v>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>110891.0</v>
-      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
       <c r="AE22" s="3"/>
       <c r="AF22" s="3"/>
       <c r="AG22" s="3"/>
       <c r="AH22" s="3"/>
     </row>
     <row r="23" spans="1:34" ht="15.75">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1897.0</v>
       </c>
-      <c r="B23" s="7" t="n">
+      <c r="B23" s="5" t="n">
         <v>155984.0</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="5" t="n">
         <v>94782.0</v>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="5" t="n">
         <v>155983.0</v>
       </c>
-      <c r="E23" s="7" t="n">
+      <c r="E23" s="5" t="n">
         <v>94782.0</v>
       </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4" t="n">
-        <v>155984.0</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>94782.0</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>155983.0</v>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>94782.0</v>
-      </c>
+      <c r="F23" s="7"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
       <c r="AE23" s="3"/>
       <c r="AF23" s="3"/>
       <c r="AG23" s="3"/>
       <c r="AH23" s="3"/>
     </row>
     <row r="24" spans="1:34" ht="15.75">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1898.0</v>
       </c>
-      <c r="B24" s="7" t="n">
+      <c r="B24" s="5" t="n">
         <v>145007.0</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="5" t="n">
         <v>106188.0</v>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="5" t="n">
         <v>145007.0</v>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="E24" s="5" t="n">
         <v>106188.0</v>
       </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4" t="n">
-        <v>145007.0</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>106188.0</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>145007.0</v>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>106188.0</v>
-      </c>
+      <c r="F24" s="7"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
       <c r="AE24" s="3"/>
       <c r="AF24" s="3"/>
       <c r="AG24" s="3"/>
       <c r="AH24" s="3"/>
     </row>
     <row r="25" spans="1:34" ht="15.75">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1899.0</v>
       </c>
-      <c r="B25" s="7" t="n">
+      <c r="B25" s="5" t="n">
         <v>158514.0</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="5" t="n">
         <v>95998.0</v>
       </c>
-      <c r="D25" s="7" t="n">
+      <c r="D25" s="5" t="n">
         <v>158514.0</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E25" s="5" t="n">
         <v>95998.0</v>
       </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4" t="n">
-        <v>158514.0</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>95998.0</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>158514.0</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>95998.0</v>
-      </c>
+      <c r="F25" s="7"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
       <c r="AE25" s="3"/>
       <c r="AF25" s="3"/>
       <c r="AG25" s="3"/>
       <c r="AH25" s="3"/>
     </row>
     <row r="26" spans="1:34" ht="15.75">
-      <c r="A26" s="6" t="n">
+      <c r="A26" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1900.0</v>
       </c>
-      <c r="B26" s="7" t="n">
+      <c r="B26" s="5" t="n">
         <v>161607.0</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="5" t="n">
         <v>94552.0</v>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D26" s="5" t="n">
         <v>161596.0</v>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E26" s="5" t="n">
         <v>94552.0</v>
       </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4" t="n">
-        <v>161607.0</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>94552.0</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>161596.0</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>94552.0</v>
-      </c>
+      <c r="F26" s="7"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
       <c r="AE26" s="3"/>
       <c r="AF26" s="3"/>
       <c r="AG26" s="3"/>
       <c r="AH26" s="3"/>
     </row>
     <row r="27" spans="1:34" ht="15.75">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1901.0</v>
       </c>
-      <c r="B27" s="7" t="n">
+      <c r="B27" s="5" t="n">
         <v>155098.0</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="5" t="n">
         <v>99805.0</v>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="D27" s="5" t="n">
         <v>155098.0</v>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="E27" s="5" t="n">
         <v>99805.0</v>
       </c>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4" t="n">
-        <v>155098.0</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>99805.0</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>155098.0</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>99805.0</v>
-      </c>
+      <c r="F27" s="7"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
       <c r="AE27" s="3"/>
       <c r="AF27" s="3"/>
       <c r="AG27" s="3"/>
       <c r="AH27" s="3"/>
     </row>
     <row r="28" spans="1:34" ht="15.75">
-      <c r="A28" s="6" t="n">
+      <c r="A28" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1902.0</v>
       </c>
-      <c r="B28" s="7" t="n">
+      <c r="B28" s="5" t="n">
         <v>159072.0</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="5" t="n">
         <v>110330.0</v>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D28" s="5" t="n">
         <v>159073.0</v>
       </c>
-      <c r="E28" s="7" t="n">
+      <c r="E28" s="5" t="n">
         <v>110330.0</v>
       </c>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4" t="n">
-        <v>159072.0</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>110330.0</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>159073.0</v>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v>110330.0</v>
-      </c>
+      <c r="F28" s="7"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
       <c r="AE28" s="3"/>
       <c r="AF28" s="3"/>
       <c r="AG28" s="3"/>
       <c r="AH28" s="3"/>
     </row>
     <row r="29" spans="1:34" ht="15.75">
-      <c r="A29" s="6" t="n">
+      <c r="A29" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1903.0</v>
       </c>
-      <c r="B29" s="7" t="n">
+      <c r="B29" s="5" t="n">
         <v>175432.0</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="5" t="n">
         <v>92715.0</v>
       </c>
-      <c r="D29" s="7" t="n">
+      <c r="D29" s="5" t="n">
         <v>175432.0</v>
       </c>
-      <c r="E29" s="7" t="n">
+      <c r="E29" s="5" t="n">
         <v>92715.0</v>
       </c>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4" t="n">
-        <v>175432.0</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>92715.0</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>175432.0</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>92715.0</v>
-      </c>
+      <c r="F29" s="7"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
       <c r="AE29" s="3"/>
       <c r="AF29" s="3"/>
       <c r="AG29" s="3"/>
       <c r="AH29" s="3"/>
     </row>
     <row r="30" spans="1:34" ht="15.75">
-      <c r="A30" s="6" t="n">
+      <c r="A30" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1904.0</v>
       </c>
-      <c r="B30" s="7" t="n">
+      <c r="B30" s="5" t="n">
         <v>171812.0</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="5" t="n">
         <v>94833.0</v>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="D30" s="5" t="n">
         <v>171812.0</v>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="E30" s="5" t="n">
         <v>94833.0</v>
       </c>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4" t="n">
-        <v>171812.0</v>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>94833.0</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>171812.0</v>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>94833.0</v>
-      </c>
+      <c r="F30" s="7"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
       <c r="AE30" s="3"/>
       <c r="AF30" s="3"/>
       <c r="AG30" s="3"/>
       <c r="AH30" s="3"/>
     </row>
     <row r="31" spans="1:34" ht="15.75">
-      <c r="A31" s="6" t="n">
+      <c r="A31" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1905.0</v>
       </c>
-      <c r="B31" s="7" t="n">
+      <c r="B31" s="5" t="n">
         <v>170441.0</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>111833.0</v>
       </c>
-      <c r="D31" s="7" t="n">
+      <c r="D31" s="5" t="n">
         <v>170430.0</v>
       </c>
-      <c r="E31" s="7" t="n">
+      <c r="E31" s="5" t="n">
         <v>111832.0</v>
       </c>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4" t="n">
-        <v>170441.0</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>111833.0</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>170430.0</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>111832.0</v>
-      </c>
+      <c r="F31" s="7"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
       <c r="AE31" s="3"/>
       <c r="AF31" s="3"/>
       <c r="AG31" s="3"/>
       <c r="AH31" s="3"/>
     </row>
     <row r="32" spans="1:34" ht="15.75">
-      <c r="A32" s="6" t="n">
+      <c r="A32" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1906.0</v>
       </c>
-      <c r="B32" s="7" t="n">
+      <c r="B32" s="5" t="n">
         <v>167155.0</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="5" t="n">
         <v>101374.0</v>
       </c>
-      <c r="D32" s="7" t="n">
+      <c r="D32" s="5" t="n">
         <v>167158.0</v>
       </c>
-      <c r="E32" s="7" t="n">
+      <c r="E32" s="5" t="n">
         <v>101374.0</v>
       </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4" t="n">
-        <v>167155.0</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>101374.0</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>167158.0</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>101374.0</v>
-      </c>
+      <c r="F32" s="7"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
       <c r="AE32" s="3"/>
       <c r="AF32" s="3"/>
       <c r="AG32" s="3"/>
       <c r="AH32" s="3"/>
     </row>
     <row r="33" spans="1:34" ht="15.75">
-      <c r="A33" s="6" t="n">
+      <c r="A33" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1907.0</v>
       </c>
-      <c r="B33" s="7" t="n">
+      <c r="B33" s="5" t="n">
         <v>177955.0</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>101440.0</v>
       </c>
-      <c r="D33" s="7" t="n">
+      <c r="D33" s="5" t="n">
         <v>177955.0</v>
       </c>
-      <c r="E33" s="7" t="n">
+      <c r="E33" s="5" t="n">
         <v>101487.0</v>
       </c>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4" t="n">
-        <v>177955.0</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>101440.0</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>177955.0</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>101487.0</v>
-      </c>
+      <c r="F33" s="7"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
       <c r="AE33" s="3"/>
       <c r="AF33" s="3"/>
       <c r="AG33" s="3"/>
       <c r="AH33" s="3"/>
     </row>
     <row r="34" spans="1:34" ht="15.75">
-      <c r="A34" s="6" t="n">
+      <c r="A34" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1908.0</v>
       </c>
-      <c r="B34" s="7" t="n">
+      <c r="B34" s="5" t="n">
         <v>169079.0</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="5" t="n">
         <v>107812.0</v>
       </c>
-      <c r="D34" s="7" t="n">
+      <c r="D34" s="5" t="n">
         <v>169080.0</v>
       </c>
-      <c r="E34" s="7" t="n">
+      <c r="E34" s="5" t="n">
         <v>107812.0</v>
       </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4" t="n">
-        <v>169079.0</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>107812.0</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>169080.0</v>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>107812.0</v>
-      </c>
+      <c r="F34" s="7"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
       <c r="AE34" s="3"/>
       <c r="AF34" s="3"/>
       <c r="AG34" s="3"/>
       <c r="AH34" s="3"/>
     </row>
     <row r="35" spans="1:34" ht="15.75">
-      <c r="A35" s="6" t="n">
+      <c r="A35" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1909.0</v>
       </c>
-      <c r="B35" s="7" t="n">
+      <c r="B35" s="5" t="n">
         <v>167968.0</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>124953.0</v>
       </c>
-      <c r="D35" s="7" t="n">
+      <c r="D35" s="5" t="n">
         <v>167966.0</v>
       </c>
-      <c r="E35" s="7" t="n">
+      <c r="E35" s="5" t="n">
         <v>124953.0</v>
       </c>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4" t="n">
-        <v>167968.0</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>124953.0</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>167966.0</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>124953.0</v>
-      </c>
+      <c r="F35" s="7"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
       <c r="AE35" s="3"/>
       <c r="AF35" s="3"/>
       <c r="AG35" s="3"/>
       <c r="AH35" s="3"/>
     </row>
     <row r="36" spans="1:34" ht="15.75">
-      <c r="A36" s="6" t="n">
+      <c r="A36" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1910.0</v>
       </c>
-      <c r="B36" s="7" t="n">
+      <c r="B36" s="5" t="n">
         <v>172542.0</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="5" t="n">
         <v>132727.0</v>
       </c>
-      <c r="D36" s="7" t="n">
+      <c r="D36" s="5" t="n">
         <v>172542.0</v>
       </c>
-      <c r="E36" s="7" t="n">
+      <c r="E36" s="5" t="n">
         <v>132727.0</v>
       </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4" t="n">
-        <v>172542.0</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>132727.0</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>172542.0</v>
-      </c>
-      <c r="J36" s="4" t="n">
-        <v>132727.0</v>
-      </c>
+      <c r="F36" s="7"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
       <c r="AE36" s="3"/>
       <c r="AF36" s="3"/>
       <c r="AG36" s="3"/>
       <c r="AH36" s="3"/>
     </row>
     <row r="37" spans="1:34" ht="15.75">
-      <c r="A37" s="6" t="n">
+      <c r="A37" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1911.0</v>
       </c>
-      <c r="B37" s="7" t="n">
+      <c r="B37" s="5" t="n">
         <v>176888.0</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="5" t="n">
         <v>105129.0</v>
       </c>
-      <c r="D37" s="7" t="n">
+      <c r="D37" s="5" t="n">
         <v>176888.0</v>
       </c>
-      <c r="E37" s="7" t="n">
+      <c r="E37" s="5" t="n">
         <v>105129.0</v>
       </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4" t="n">
-        <v>176888.0</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>105129.0</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>176888.0</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>105129.0</v>
-      </c>
+      <c r="F37" s="7"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
       <c r="AE37" s="3"/>
       <c r="AF37" s="3"/>
       <c r="AG37" s="3"/>
       <c r="AH37" s="3"/>
     </row>
     <row r="38" spans="1:34" ht="15.75">
-      <c r="A38" s="6" t="n">
+      <c r="A38" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1912.0</v>
       </c>
-      <c r="B38" s="7" t="n">
+      <c r="B38" s="5" t="n">
         <v>176717.0</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="5" t="n">
         <v>96620.0</v>
       </c>
-      <c r="D38" s="7" t="n">
+      <c r="D38" s="5" t="n">
         <v>176717.0</v>
       </c>
-      <c r="E38" s="7" t="n">
+      <c r="E38" s="5" t="n">
         <v>96620.0</v>
       </c>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4" t="n">
-        <v>176717.0</v>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>96620.0</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>176717.0</v>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>96620.0</v>
-      </c>
+      <c r="F38" s="7"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
       <c r="AE38" s="3"/>
       <c r="AF38" s="3"/>
       <c r="AG38" s="3"/>
       <c r="AH38" s="3"/>
     </row>
     <row r="39" spans="1:34" ht="15.75">
-      <c r="A39" s="6" t="n">
+      <c r="A39" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1913.0</v>
       </c>
-      <c r="B39" s="7" t="n">
+      <c r="B39" s="5" t="n">
         <v>175310.0</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="5" t="n">
         <v>109194.0</v>
       </c>
-      <c r="D39" s="7" t="n">
+      <c r="D39" s="5" t="n">
         <v>175310.0</v>
       </c>
-      <c r="E39" s="7" t="n">
+      <c r="E39" s="5" t="n">
         <v>109194.0</v>
       </c>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4" t="n">
-        <v>175310.0</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>109194.0</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>175310.0</v>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>109194.0</v>
-      </c>
+      <c r="F39" s="7"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
     </row>
     <row r="40" spans="1:34" ht="15.75">
-      <c r="A40" s="6" t="n">
+      <c r="A40" s="10" t="n">
         <f t="shared" si="0"/>
         <v>1914.0</v>
       </c>
-      <c r="B40" s="7" t="n">
+      <c r="B40" s="5" t="n">
         <v>179164.0</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="5" t="n">
         <v>110219.0</v>
       </c>
-      <c r="D40" s="7" t="n">
+      <c r="D40" s="5" t="n">
         <v>179175.0</v>
       </c>
-      <c r="E40" s="7" t="n">
+      <c r="E40" s="5" t="n">
         <v>110219.0</v>
       </c>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4" t="n">
-        <v>179164.0</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>110219.0</v>
-      </c>
-      <c r="I40" s="4" t="n">
-        <v>179175.0</v>
-      </c>
-      <c r="J40" s="4" t="n">
-        <v>110219.0</v>
-      </c>
+      <c r="F40" s="7"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
     </row>
     <row r="41" spans="1:34" ht="15.75">
       <c r="A41" s="4"/>
@@ -4509,7 +4253,8 @@
     <mergeCell ref="G3:J3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/rtss-pre1917/charts/birth-death-counts/Воронежская.xlsx
+++ b/rtss-pre1917/charts/birth-death-counts/Воронежская.xlsx
@@ -3192,14 +3192,14 @@
   <sheetData>
     <row r="1" spans="1:34" ht="21">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
